--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92576014886</v>
+        <v>46157.93121191642</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93121191642</v>
+        <v>46157.93186853781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93186853781</v>
+        <v>46157.93407362213</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93407362213</v>
+        <v>46157.9372549194</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9372549194</v>
+        <v>46158.28222965849</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28222965849</v>
+        <v>46158.29712388982</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29712388982</v>
+        <v>46158.29823116137</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29823116137</v>
+        <v>46158.33393994236</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33393994236</v>
+        <v>46158.36863750368</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Цуканов- водитель/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36863750368</v>
+        <v>46158.37294737839</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
